--- a/finance/_sheet_out/indrive_unit_econ.xlsx
+++ b/finance/_sheet_out/indrive_unit_econ.xlsx
@@ -53,8 +53,8 @@
     <definedName name="load_sel">'Assumptions'!$B$49</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$50</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$5</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$16</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$16</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$19</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2348,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA16"/>
+  <dimension ref="A1:BA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3123,25 +3123,17 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
+          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>6</v>
+        <v>4.79</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" s="34" t="inlineStr">
-        <is>
-          <t>T1/T2</t>
-        </is>
-      </c>
-      <c r="G6" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
       <c r="H6" s="20" t="n">
         <v>1</v>
       </c>
@@ -3246,16 +3238,16 @@
         <v/>
       </c>
       <c r="AH6" s="33" t="n">
-        <v>278607</v>
+        <v>6100556</v>
       </c>
       <c r="AI6" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AJ6" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med-low</t>
         </is>
       </c>
       <c r="AK6" s="41" t="n">
@@ -3302,19 +3294,15 @@
         <f>IF(((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6)))</f>
         <v/>
       </c>
-      <c r="AY6" s="46" t="inlineStr">
-        <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
-        </is>
-      </c>
+      <c r="AY6" s="46" t="n"/>
       <c r="AZ6" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
         </is>
       </c>
       <c r="BA6" s="34" t="inlineStr">
         <is>
-          <t>rn-369ef0eb69d9</t>
+          <t>rn-floripa-r4-PROV</t>
         </is>
       </c>
     </row>
@@ -3331,25 +3319,17 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
+          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.199999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>T1/T2</t>
-        </is>
-      </c>
-      <c r="G7" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
       <c r="H7" s="20" t="n">
         <v>1</v>
       </c>
@@ -3454,16 +3434,16 @@
         <v/>
       </c>
       <c r="AH7" s="33" t="n">
-        <v>1170652</v>
+        <v>3890964</v>
       </c>
       <c r="AI7" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AJ7" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med-low</t>
         </is>
       </c>
       <c r="AK7" s="41" t="n">
@@ -3510,46 +3490,50 @@
         <f>IF(((T7*pax_cap*load_full*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0)))-(((battery/range_nm)*D7*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0))*VLOOKUP(B7,country_opex,3,FALSE))+W7+X7+Y7+Z7+AA7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((T7*pax_cap*load_full*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0)))-(((battery/range_nm)*D7*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0))*VLOOKUP(B7,country_opex,3,FALSE))+W7+X7+Y7+Z7+AA7)))</f>
         <v/>
       </c>
-      <c r="AY7" s="46" t="inlineStr">
-        <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
-        </is>
-      </c>
+      <c r="AY7" s="46" t="n"/>
       <c r="AZ7" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
         </is>
       </c>
       <c r="BA7" s="34" t="inlineStr">
         <is>
-          <t>rn-00bb6ded4be5</t>
+          <t>rn-floripa-r3-PROV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H8" s="20" t="n">
         <v>1</v>
       </c>
@@ -3654,12 +3638,20 @@
         <v/>
       </c>
       <c r="AH8" s="33" t="n">
-        <v>187512</v>
-      </c>
-      <c r="AI8" s="34" t="n"/>
-      <c r="AJ8" s="34" t="n"/>
+        <v>278607</v>
+      </c>
+      <c r="AI8" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ8" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AK8" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL8" s="36">
         <f>IF(AH8="","",AH8*AK8)</f>
@@ -3702,38 +3694,54 @@
         <f>IF(((T8*pax_cap*load_full*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0)))-(((battery/range_nm)*D8*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0))*VLOOKUP(B8,country_opex,3,FALSE))+W8+X8+Y8+Z8+AA8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((T8*pax_cap*load_full*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0)))-(((battery/range_nm)*D8*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0))*VLOOKUP(B8,country_opex,3,FALSE))+W8+X8+Y8+Z8+AA8)))</f>
         <v/>
       </c>
-      <c r="AY8" s="46" t="n"/>
-      <c r="AZ8" s="46" t="n"/>
+      <c r="AY8" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ8" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
       <c r="BA8" s="34" t="inlineStr">
         <is>
-          <t>rn-b06f6971ed47</t>
+          <t>rn-369ef0eb69d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="34" t="n"/>
-      <c r="G9" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H9" s="20" t="n">
         <v>1</v>
       </c>
@@ -3838,12 +3846,20 @@
         <v/>
       </c>
       <c r="AH9" s="33" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AI9" s="34" t="n"/>
-      <c r="AJ9" s="34" t="n"/>
+        <v>1170652</v>
+      </c>
+      <c r="AI9" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ9" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AK9" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL9" s="36">
         <f>IF(AH9="","",AH9*AK9)</f>
@@ -3886,144 +3902,728 @@
         <f>IF(((T9*pax_cap*load_full*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0)))-(((battery/range_nm)*D9*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0))*VLOOKUP(B9,country_opex,3,FALSE))+W9+X9+Y9+Z9+AA9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((T9*pax_cap*load_full*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0)))-(((battery/range_nm)*D9*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0))*VLOOKUP(B9,country_opex,3,FALSE))+W9+X9+Y9+Z9+AA9)))</f>
         <v/>
       </c>
-      <c r="AY9" s="46" t="n"/>
-      <c r="AZ9" s="46" t="n"/>
+      <c r="AY9" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ9" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
       <c r="BA9" s="34" t="inlineStr">
         <is>
+          <t>rn-00bb6ded4be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Angra dos Reis Terminal (Costa Verde) → Abraão Terminal (Ilha Grande)</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="35">
+        <f>60*D10/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>IF(B10="South Korea",D10/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="35">
+        <f>IF(B10="South Korea",I10+korea_turn_min+korea_dwell_min+J10,I10+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L10" s="36">
+        <f>IF(B10="South Korea",FLOOR(60*korea_service_hr/K10,1),MIN(15,FLOOR(60*service_hr/K10,1)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H10)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H10)/2,0),ROUND((365*mech_uptime*H10),0))</f>
+        <v/>
+      </c>
+      <c r="N10" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O10" s="37">
+        <f>IF(AND(B10="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P10" s="36">
+        <f>IF(ABS(MOD(ABS((L10*M10*O10)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*O10)/2,0),ROUND((L10*M10*O10),0))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="37">
+        <f>IF(AND(B10="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R10" s="38">
+        <f>pax_cap*Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="36">
+        <f>R10*P10</f>
+        <v/>
+      </c>
+      <c r="T10" s="39">
+        <f>E10*discount</f>
+        <v/>
+      </c>
+      <c r="U10" s="40">
+        <f>T10*S10</f>
+        <v/>
+      </c>
+      <c r="V10" s="40">
+        <f>(battery/range_nm)*D10*P10*VLOOKUP(B10,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W10" s="40">
+        <f>VLOOKUP(B10,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X10" s="40">
+        <f>VLOOKUP(B10,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z10" s="40">
+        <f>VLOOKUP(B10,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA10" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB10" s="40">
+        <f>V10+W10+X10+Y10+Z10+AA10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="40">
+        <f>VLOOKUP(B10,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD10" s="40">
+        <f>U10-AB10</f>
+        <v/>
+      </c>
+      <c r="AE10" s="37">
+        <f>IF(U10=0,"",AD10/U10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="38">
+        <f>IF(AD10&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/AD10)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="35">
+        <f>((D10*P10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*P10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH10" s="33" t="n">
+        <v>207993</v>
+      </c>
+      <c r="AI10" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ10" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK10" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL10" s="36">
+        <f>IF(AH10="","",AH10*AK10)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="36">
+        <f>IF(OR(AH10="",S10=0),"",MIN(IF(AU10="",9.9E+99,AU10),FLOOR(AL10/S10,1)))</f>
+        <v/>
+      </c>
+      <c r="AN10" s="40">
+        <f>IF(AM10="","",AM10*IF(ABS(MOD(ABS((U10)),1)-0.5)&lt;1E-9,2*ROUND((U10)/2,0),ROUND((U10),0)))</f>
+        <v/>
+      </c>
+      <c r="AO10" s="38">
+        <f>IF(OR(AH10="",S10=0),"",MIN(IF(AU10="",9.9E+99,AU10),AL10/S10))</f>
+        <v/>
+      </c>
+      <c r="AP10" s="40">
+        <f>IF(AO10="","",AO10*IF(B10="South Korea",IF(ABS(MOD(ABS((U10)),1)-0.5)&lt;1E-9,2*ROUND((U10)/2,0),ROUND((U10),0)),U10))</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="42" t="n"/>
+      <c r="AR10" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS10" s="43" t="n"/>
+      <c r="AT10" s="43" t="n"/>
+      <c r="AU10" s="44" t="n"/>
+      <c r="AV10" s="45">
+        <f>IF(((T10*pax_cap*load_thin*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*load_thin*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AW10" s="45">
+        <f>IF(((T10*pax_cap*IF(B10="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*IF(B10="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AX10" s="45">
+        <f>IF(((T10*pax_cap*load_full*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*load_full*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="46" t="inlineStr">
+        <is>
+          <t>AGETRANSP / CCR Barcas Costa Verde published tariff</t>
+        </is>
+      </c>
+      <c r="AZ10" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
+      <c r="BA10" s="34" t="inlineStr">
+        <is>
+          <t>rn-angra-abraao-PROV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="35">
+        <f>60*D11/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J11" s="35">
+        <f>IF(B11="South Korea",D11/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="35">
+        <f>IF(B11="South Korea",I11+korea_turn_min+korea_dwell_min+J11,I11+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L11" s="36">
+        <f>IF(B11="South Korea",FLOOR(60*korea_service_hr/K11,1),MIN(15,FLOOR(60*service_hr/K11,1)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H11)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H11)/2,0),ROUND((365*mech_uptime*H11),0))</f>
+        <v/>
+      </c>
+      <c r="N11" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O11" s="37">
+        <f>IF(AND(B11="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P11" s="36">
+        <f>IF(ABS(MOD(ABS((L11*M11*O11)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*O11)/2,0),ROUND((L11*M11*O11),0))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="37">
+        <f>IF(AND(B11="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R11" s="38">
+        <f>pax_cap*Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="36">
+        <f>R11*P11</f>
+        <v/>
+      </c>
+      <c r="T11" s="39">
+        <f>E11*discount</f>
+        <v/>
+      </c>
+      <c r="U11" s="40">
+        <f>T11*S11</f>
+        <v/>
+      </c>
+      <c r="V11" s="40">
+        <f>(battery/range_nm)*D11*P11*VLOOKUP(B11,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W11" s="40">
+        <f>VLOOKUP(B11,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X11" s="40">
+        <f>VLOOKUP(B11,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z11" s="40">
+        <f>VLOOKUP(B11,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA11" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB11" s="40">
+        <f>V11+W11+X11+Y11+Z11+AA11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="40">
+        <f>VLOOKUP(B11,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD11" s="40">
+        <f>U11-AB11</f>
+        <v/>
+      </c>
+      <c r="AE11" s="37">
+        <f>IF(U11=0,"",AD11/U11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="38">
+        <f>IF(AD11&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/AD11)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="35">
+        <f>((D11*P11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*P11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH11" s="33" t="n">
+        <v>187512</v>
+      </c>
+      <c r="AI11" s="34" t="n"/>
+      <c r="AJ11" s="34" t="n"/>
+      <c r="AK11" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL11" s="36">
+        <f>IF(AH11="","",AH11*AK11)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="36">
+        <f>IF(OR(AH11="",S11=0),"",MIN(IF(AU11="",9.9E+99,AU11),FLOOR(AL11/S11,1)))</f>
+        <v/>
+      </c>
+      <c r="AN11" s="40">
+        <f>IF(AM11="","",AM11*IF(ABS(MOD(ABS((U11)),1)-0.5)&lt;1E-9,2*ROUND((U11)/2,0),ROUND((U11),0)))</f>
+        <v/>
+      </c>
+      <c r="AO11" s="38">
+        <f>IF(OR(AH11="",S11=0),"",MIN(IF(AU11="",9.9E+99,AU11),AL11/S11))</f>
+        <v/>
+      </c>
+      <c r="AP11" s="40">
+        <f>IF(AO11="","",AO11*IF(B11="South Korea",IF(ABS(MOD(ABS((U11)),1)-0.5)&lt;1E-9,2*ROUND((U11)/2,0),ROUND((U11),0)),U11))</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="42" t="n"/>
+      <c r="AR11" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS11" s="43" t="n"/>
+      <c r="AT11" s="43" t="n"/>
+      <c r="AU11" s="44" t="n"/>
+      <c r="AV11" s="45">
+        <f>IF(((T11*pax_cap*load_thin*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*load_thin*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AW11" s="45">
+        <f>IF(((T11*pax_cap*IF(B11="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*IF(B11="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AX11" s="45">
+        <f>IF(((T11*pax_cap*load_full*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*load_full*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="46" t="n"/>
+      <c r="AZ11" s="46" t="n"/>
+      <c r="BA11" s="34" t="inlineStr">
+        <is>
+          <t>rn-b06f6971ed47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="35">
+        <f>60*D12/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>IF(B12="South Korea",D12/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="35">
+        <f>IF(B12="South Korea",I12+korea_turn_min+korea_dwell_min+J12,I12+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L12" s="36">
+        <f>IF(B12="South Korea",FLOOR(60*korea_service_hr/K12,1),MIN(15,FLOOR(60*service_hr/K12,1)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H12)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H12)/2,0),ROUND((365*mech_uptime*H12),0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O12" s="37">
+        <f>IF(AND(B12="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P12" s="36">
+        <f>IF(ABS(MOD(ABS((L12*M12*O12)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*O12)/2,0),ROUND((L12*M12*O12),0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="37">
+        <f>IF(AND(B12="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R12" s="38">
+        <f>pax_cap*Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="36">
+        <f>R12*P12</f>
+        <v/>
+      </c>
+      <c r="T12" s="39">
+        <f>E12*discount</f>
+        <v/>
+      </c>
+      <c r="U12" s="40">
+        <f>T12*S12</f>
+        <v/>
+      </c>
+      <c r="V12" s="40">
+        <f>(battery/range_nm)*D12*P12*VLOOKUP(B12,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W12" s="40">
+        <f>VLOOKUP(B12,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X12" s="40">
+        <f>VLOOKUP(B12,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z12" s="40">
+        <f>VLOOKUP(B12,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA12" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB12" s="40">
+        <f>V12+W12+X12+Y12+Z12+AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="40">
+        <f>VLOOKUP(B12,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD12" s="40">
+        <f>U12-AB12</f>
+        <v/>
+      </c>
+      <c r="AE12" s="37">
+        <f>IF(U12=0,"",AD12/U12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="38">
+        <f>IF(AD12&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/AD12)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="35">
+        <f>((D12*P12/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D12*P12*VLOOKUP(B12,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH12" s="33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AI12" s="34" t="n"/>
+      <c r="AJ12" s="34" t="n"/>
+      <c r="AK12" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL12" s="36">
+        <f>IF(AH12="","",AH12*AK12)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="36">
+        <f>IF(OR(AH12="",S12=0),"",MIN(IF(AU12="",9.9E+99,AU12),FLOOR(AL12/S12,1)))</f>
+        <v/>
+      </c>
+      <c r="AN12" s="40">
+        <f>IF(AM12="","",AM12*IF(ABS(MOD(ABS((U12)),1)-0.5)&lt;1E-9,2*ROUND((U12)/2,0),ROUND((U12),0)))</f>
+        <v/>
+      </c>
+      <c r="AO12" s="38">
+        <f>IF(OR(AH12="",S12=0),"",MIN(IF(AU12="",9.9E+99,AU12),AL12/S12))</f>
+        <v/>
+      </c>
+      <c r="AP12" s="40">
+        <f>IF(AO12="","",AO12*IF(B12="South Korea",IF(ABS(MOD(ABS((U12)),1)-0.5)&lt;1E-9,2*ROUND((U12)/2,0),ROUND((U12),0)),U12))</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="42" t="n"/>
+      <c r="AR12" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS12" s="43" t="n"/>
+      <c r="AT12" s="43" t="n"/>
+      <c r="AU12" s="44" t="n"/>
+      <c r="AV12" s="45">
+        <f>IF(((T12*pax_cap*load_thin*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*load_thin*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AW12" s="45">
+        <f>IF(((T12*pax_cap*IF(B12="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*IF(B12="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AX12" s="45">
+        <f>IF(((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="46" t="n"/>
+      <c r="AZ12" s="46" t="n"/>
+      <c r="BA12" s="34" t="inlineStr">
+        <is>
           <t>rn-c16a1627130f</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="U10" s="48">
-        <f>SUM(U4:U9)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="48">
-        <f>SUM(AD4:AD9)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="49">
-        <f>IF(U10=0,"",AD10/U10)</f>
-        <v/>
-      </c>
-      <c r="AM10" s="50">
-        <f>SUM(AM4:AM9)</f>
-        <v/>
-      </c>
-      <c r="AN10" s="48">
-        <f>SUM(AN4:AN9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="U13" s="48">
+        <f>SUM(U4:U12)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="48">
+        <f>SUM(AD4:AD12)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="49">
+        <f>IF(U13=0,"",AD13/U13)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="50">
+        <f>SUM(AM4:AM12)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="48">
+        <f>SUM(AN4:AN12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Indrive Brazil</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>per_corridor_floor</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="51">
-        <f>SUMIFS(AM4:AM9,A4:A9,"Indrive Brazil",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E14" s="52">
-        <f>SUMIFS(AN4:AN9,A4:A9,"Indrive Brazil",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="D17" s="51">
+        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E17" s="52">
+        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Indrive Egypt</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>two luxury-belt captive routes on labeled destination-pool demand at ~90% floor capture; three held</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="51">
-        <f>SUMIFS(AM4:AM9,A4:A9,"Indrive Egypt",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E15" s="52">
-        <f>SUMIFS(AN4:AN9,A4:A9,"Indrive Egypt",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="D18" s="51">
+        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D16" s="50">
-        <f>SUM(D14:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="48">
-        <f>SUM(E14:E15)</f>
+      <c r="D19" s="50">
+        <f>SUM(D17:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="48">
+        <f>SUM(E17:E18)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:L15"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A12:L12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4192,12 +4792,12 @@
         </is>
       </c>
       <c r="C11" s="53">
-        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$9="Grounded"),'Corridor economics'!$AH$4:$AH$9,'Corridor economics'!$E$4:$E$9),0))</f>
+        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0))</f>
         <v/>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>New-entrant ~12% share of today's pool (= the published floor).</t>
+          <t>New-entrant ~11% share of today's pool (= the published floor).</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4858,7 @@
         </is>
       </c>
       <c r="C16" s="52">
-        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$9="Grounded"),'Corridor economics'!$AH$4:$AH$9,'Corridor economics'!$E$4:$E$9),0)</f>
+        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0)</f>
         <v/>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -4270,7 +4870,7 @@
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>SOM full network (~12% capture, today, +greenfield)</t>
+          <t>SOM full network (~11% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="52">
@@ -4287,7 +4887,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Floor posture (~12% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~11% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>

--- a/finance/_sheet_out/indrive_unit_econ.xlsx
+++ b/finance/_sheet_out/indrive_unit_econ.xlsx
@@ -3123,11 +3123,11 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>20</v>
@@ -3238,7 +3238,7 @@
         <v/>
       </c>
       <c r="AH6" s="33" t="n">
-        <v>6100556</v>
+        <v>3890964</v>
       </c>
       <c r="AI6" s="34" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="BA6" s="34" t="inlineStr">
         <is>
-          <t>rn-floripa-r4-PROV</t>
+          <t>rn-36dcca92d821</t>
         </is>
       </c>
     </row>
@@ -3319,11 +3319,11 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>4.99</v>
+        <v>5.15</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>20</v>
@@ -3434,7 +3434,7 @@
         <v/>
       </c>
       <c r="AH7" s="33" t="n">
-        <v>3890964</v>
+        <v>6100556</v>
       </c>
       <c r="AI7" s="34" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="BA7" s="34" t="inlineStr">
         <is>
-          <t>rn-floripa-r3-PROV</t>
+          <t>rn-7d157e1300da</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="BA10" s="34" t="inlineStr">
         <is>
-          <t>rn-angra-abraao-PROV</t>
+          <t>rn-7ec802385553</t>
         </is>
       </c>
     </row>

--- a/finance/_sheet_out/indrive_unit_econ.xlsx
+++ b/finance/_sheet_out/indrive_unit_econ.xlsx
@@ -53,8 +53,8 @@
     <definedName name="load_sel">'Assumptions'!$B$49</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$50</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$5</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$19</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$19</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$28</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -329,6 +329,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2348,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA19"/>
+  <dimension ref="A1:BA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2707,23 +2713,23 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Arariboia Terminal (Niterói)</t>
+          <t>Terminal da Balsa Ponta da Praia (Santos) → Terminal da Balsa Guarujá (Av. Adhemar de Barros)</t>
         </is>
       </c>
       <c r="D4" s="33" t="n">
-        <v>2.7</v>
+        <v>0.25</v>
       </c>
       <c r="E4" s="27" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F4" s="34" t="inlineStr">
         <is>
-          <t>T1/T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G4" s="34" t="inlineStr">
         <is>
-          <t>med-low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H4" s="20" t="n">
@@ -2830,16 +2836,16 @@
         <v/>
       </c>
       <c r="AH4" s="33" t="n">
-        <v>10848719</v>
+        <v>5584500</v>
       </c>
       <c r="AI4" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2/T3 (annualized from crossing-specific dailies)</t>
         </is>
       </c>
       <c r="AJ4" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
       <c r="AK4" s="41" t="n">
@@ -2888,17 +2894,17 @@
       </c>
       <c r="AY4" s="46" t="inlineStr">
         <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+          <t>Acqua Vias PPP terms / state announcement</t>
         </is>
       </c>
       <c r="AZ4" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>Crossing-specific daily counts: ~7.6k pedestrians + ~7.7k cyclists = 15,300/day (Travessia Santos–Guarujá, A Tribuna basis, corroborated by DH system datasheets: system-wide 57k users/day across 8 crossings, Santos–Guarujá the busiest).</t>
         </is>
       </c>
       <c r="BA4" s="34" t="inlineStr">
         <is>
-          <t>rn-1886629dbf0c</t>
+          <t>rn-07cdabeba7a9</t>
         </is>
       </c>
     </row>
@@ -2915,25 +2921,17 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Charitas Terminal (Niterói, fast catamaran)</t>
+          <t>Terminal de Passageiros Santos Centro / Praça da República → Terminal de Passageiros Vicente de Carvalho (Guarujá)</t>
         </is>
       </c>
       <c r="D5" s="33" t="n">
-        <v>4.4</v>
+        <v>0.66</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>T1/T2</t>
-        </is>
-      </c>
-      <c r="G5" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n"/>
       <c r="H5" s="20" t="n">
         <v>1</v>
       </c>
@@ -3037,19 +3035,9 @@
         <f>((D5*P5/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D5*P5*VLOOKUP(B5,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AH5" s="33" t="n">
-        <v>825637</v>
-      </c>
-      <c r="AI5" s="34" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AJ5" s="34" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
+      <c r="AH5" s="33" t="n"/>
+      <c r="AI5" s="34" t="n"/>
+      <c r="AJ5" s="34" t="n"/>
       <c r="AK5" s="41" t="n">
         <v>0.1</v>
       </c>
@@ -3076,7 +3064,7 @@
       <c r="AQ5" s="42" t="n"/>
       <c r="AR5" s="34" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AS5" s="43" t="n"/>
@@ -3094,19 +3082,11 @@
         <f>IF(((T5*pax_cap*load_full*IF(ABS(MOD(ABS((L5*M5*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L5*M5*revleg_full)/2,0),ROUND((L5*M5*revleg_full),0)))-(((battery/range_nm)*D5*IF(ABS(MOD(ABS((L5*M5*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L5*M5*revleg_full)/2,0),ROUND((L5*M5*revleg_full),0))*VLOOKUP(B5,country_opex,3,FALSE))+W5+X5+Y5+Z5+AA5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((T5*pax_cap*load_full*IF(ABS(MOD(ABS((L5*M5*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L5*M5*revleg_full)/2,0),ROUND((L5*M5*revleg_full),0)))-(((battery/range_nm)*D5*IF(ABS(MOD(ABS((L5*M5*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L5*M5*revleg_full)/2,0),ROUND((L5*M5*revleg_full),0))*VLOOKUP(B5,country_opex,3,FALSE))+W5+X5+Y5+Z5+AA5)))</f>
         <v/>
       </c>
-      <c r="AY5" s="46" t="inlineStr">
-        <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
-        </is>
-      </c>
-      <c r="AZ5" s="46" t="inlineStr">
-        <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
-        </is>
-      </c>
+      <c r="AY5" s="46" t="n"/>
+      <c r="AZ5" s="46" t="n"/>
       <c r="BA5" s="34" t="inlineStr">
         <is>
-          <t>rn-80f0d0ebe0bd</t>
+          <t>rn-3a67668a48a5</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3103,25 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>São Sebastião Ferry Terminal (Balsa) → Ilhabela Ferry Terminal (Barra Velha)</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>4.77</v>
+        <v>1.18</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="H6" s="20" t="n">
         <v>1</v>
       </c>
@@ -3238,16 +3226,16 @@
         <v/>
       </c>
       <c r="AH6" s="33" t="n">
-        <v>3890964</v>
+        <v>1493447</v>
       </c>
       <c r="AI6" s="34" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3 (modeled from T1 official inputs)</t>
         </is>
       </c>
       <c r="AJ6" s="34" t="inlineStr">
         <is>
-          <t>med-low</t>
+          <t>med</t>
         </is>
       </c>
       <c r="AK6" s="41" t="n">
@@ -3294,15 +3282,19 @@
         <f>IF(((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6)))</f>
         <v/>
       </c>
-      <c r="AY6" s="46" t="n"/>
+      <c r="AY6" s="46" t="inlineStr">
+        <is>
+          <t>Prefeitura de Ilhabela Aquabus tariff + Jan-2025 decree</t>
+        </is>
+      </c>
       <c r="AZ6" s="46" t="inlineStr">
         <is>
-          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
+          <t>Semil-SP official figures: H1-2024 system users 9,647,595 (8 litoral crossings); crossing share 15% of trips (Semil, Jul 2024); summer-operation mode split 593,073 ped+cyc of 1.15M users (15 Dec 2024–10 Mar 2025).</t>
         </is>
       </c>
       <c r="BA6" s="34" t="inlineStr">
         <is>
-          <t>rn-36dcca92d821</t>
+          <t>rn-1d1a798e7d82</t>
         </is>
       </c>
     </row>
@@ -3319,14 +3311,14 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>Terminal Aquaviário Público de Pontal do Sul → Ilha do Mel — Trapiche de Encantadas</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>5.15</v>
+        <v>2.25</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7" s="34" t="n"/>
       <c r="G7" s="34" t="n"/>
@@ -3433,19 +3425,9 @@
         <f>((D7*P7/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D7*P7*VLOOKUP(B7,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AH7" s="33" t="n">
-        <v>6100556</v>
-      </c>
-      <c r="AI7" s="34" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AJ7" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+      <c r="AH7" s="33" t="n"/>
+      <c r="AI7" s="34" t="n"/>
+      <c r="AJ7" s="34" t="n"/>
       <c r="AK7" s="41" t="n">
         <v>0.1</v>
       </c>
@@ -3472,7 +3454,7 @@
       <c r="AQ7" s="42" t="n"/>
       <c r="AR7" s="34" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AS7" s="43" t="n"/>
@@ -3491,14 +3473,10 @@
         <v/>
       </c>
       <c r="AY7" s="46" t="n"/>
-      <c r="AZ7" s="46" t="inlineStr">
-        <is>
-          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
-        </is>
-      </c>
+      <c r="AZ7" s="46" t="n"/>
       <c r="BA7" s="34" t="inlineStr">
         <is>
-          <t>rn-7d157e1300da</t>
+          <t>rn-f405c4df3ed2</t>
         </is>
       </c>
     </row>
@@ -3515,11 +3493,11 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
+          <t>Praça XV Terminal (central Rio) → Arariboia Terminal (Niterói)</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>28</v>
@@ -3638,7 +3616,7 @@
         <v/>
       </c>
       <c r="AH8" s="33" t="n">
-        <v>278607</v>
+        <v>10848719</v>
       </c>
       <c r="AI8" s="34" t="inlineStr">
         <is>
@@ -3706,7 +3684,7 @@
       </c>
       <c r="BA8" s="34" t="inlineStr">
         <is>
-          <t>rn-369ef0eb69d9</t>
+          <t>rn-1886629dbf0c</t>
         </is>
       </c>
     </row>
@@ -3723,23 +3701,23 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
+          <t>Estação Governador Albuíno Azeredo (Aquaviário da Prainha, Vila Velha) → Estação Prefeito Setembrino Pelissari (Aquaviário da Praça do Papa, Vitória)</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>9.199999999999999</v>
+        <v>3.49</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>T1/T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G9" s="34" t="inlineStr">
         <is>
-          <t>med-low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H9" s="20" t="n">
@@ -3846,7 +3824,7 @@
         <v/>
       </c>
       <c r="AH9" s="33" t="n">
-        <v>1170652</v>
+        <v>500000</v>
       </c>
       <c r="AI9" s="34" t="inlineStr">
         <is>
@@ -3904,17 +3882,17 @@
       </c>
       <c r="AY9" s="46" t="inlineStr">
         <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+          <t>CETURB-ES published tariff (R$5.10 ≈ US$1.01)</t>
         </is>
       </c>
       <c r="AZ9" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>SEMOBI official: 'Aquaviário comemora um ano de atividade com marca de 500 mil passageiros'; corroborated by SEP Mar-2026 (&gt;1.2M cumulative through Dec 2025 ⇒ ~500–550k/yr run-rate).</t>
         </is>
       </c>
       <c r="BA9" s="34" t="inlineStr">
         <is>
-          <t>rn-00bb6ded4be5</t>
+          <t>rn-1ff034e787c5</t>
         </is>
       </c>
     </row>
@@ -3931,14 +3909,14 @@
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>Angra dos Reis Terminal (Costa Verde) → Abraão Terminal (Ilha Grande)</t>
+          <t>Terminal Aquaviário Público de Pontal do Sul → Ilha do Mel — Trapiche de Nova Brasília</t>
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>13</v>
+        <v>3.82</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F10" s="34" t="inlineStr">
         <is>
@@ -3947,7 +3925,7 @@
       </c>
       <c r="G10" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
       <c r="H10" s="20" t="n">
@@ -4054,16 +4032,16 @@
         <v/>
       </c>
       <c r="AH10" s="33" t="n">
-        <v>207993</v>
+        <v>383162</v>
       </c>
       <c r="AI10" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1/T2</t>
         </is>
       </c>
       <c r="AJ10" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med-high</t>
         </is>
       </c>
       <c r="AK10" s="41" t="n">
@@ -4112,41 +4090,41 @@
       </c>
       <c r="AY10" s="46" t="inlineStr">
         <is>
-          <t>AGETRANSP / CCR Barcas Costa Verde published tariff</t>
+          <t>AGEPAR homologated tariff table (Mar 2023); 2025/26 season market pricing</t>
         </is>
       </c>
       <c r="AZ10" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>Abaline (official crossing operators' association) via Gazeta do Povo; corroborated by IAT park visitation 247,020 (2025, most-visited state park in Paraná; +21% vs 2024).</t>
         </is>
       </c>
       <c r="BA10" s="34" t="inlineStr">
         <is>
-          <t>rn-7ec802385553</t>
+          <t>rn-d0bee9173524</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+          <t>Terminal Turístico Náutico da Bahia (Comércio) → Terminal Marítimo de Mar Grande (Vera Cruz)</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>6.6</v>
+        <v>4.14</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F11" s="34" t="n"/>
       <c r="G11" s="34" t="n"/>
@@ -4253,13 +4231,11 @@
         <f>((D11*P11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*P11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AH11" s="33" t="n">
-        <v>187512</v>
-      </c>
+      <c r="AH11" s="33" t="n"/>
       <c r="AI11" s="34" t="n"/>
       <c r="AJ11" s="34" t="n"/>
       <c r="AK11" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL11" s="36">
         <f>IF(AH11="","",AH11*AK11)</f>
@@ -4284,7 +4260,7 @@
       <c r="AQ11" s="42" t="n"/>
       <c r="AR11" s="34" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AS11" s="43" t="n"/>
@@ -4306,34 +4282,42 @@
       <c r="AZ11" s="46" t="n"/>
       <c r="BA11" s="34" t="inlineStr">
         <is>
-          <t>rn-b06f6971ed47</t>
+          <t>rn-c6d5aa38e4dc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+          <t>Praça XV Terminal (central Rio) → Charitas Terminal (Niterói, fast catamaran)</t>
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>11.7</v>
+        <v>4.4</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="34" t="n"/>
-      <c r="G12" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H12" s="20" t="n">
         <v>1</v>
       </c>
@@ -4438,12 +4422,20 @@
         <v/>
       </c>
       <c r="AH12" s="33" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AI12" s="34" t="n"/>
-      <c r="AJ12" s="34" t="n"/>
+        <v>825637</v>
+      </c>
+      <c r="AI12" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ12" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AK12" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL12" s="36">
         <f>IF(AH12="","",AH12*AK12)</f>
@@ -4486,143 +4478,1940 @@
         <f>IF(((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
         <v/>
       </c>
-      <c r="AY12" s="46" t="n"/>
-      <c r="AZ12" s="46" t="n"/>
+      <c r="AY12" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ12" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
       <c r="BA12" s="34" t="inlineStr">
         <is>
+          <t>rn-80f0d0ebe0bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="35">
+        <f>60*D13/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J13" s="35">
+        <f>IF(B13="South Korea",D13/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="35">
+        <f>IF(B13="South Korea",I13+korea_turn_min+korea_dwell_min+J13,I13+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L13" s="36">
+        <f>IF(B13="South Korea",FLOOR(60*korea_service_hr/K13,1),MIN(15,FLOOR(60*service_hr/K13,1)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H13)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H13)/2,0),ROUND((365*mech_uptime*H13),0))</f>
+        <v/>
+      </c>
+      <c r="N13" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O13" s="37">
+        <f>IF(AND(B13="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P13" s="36">
+        <f>IF(ABS(MOD(ABS((L13*M13*O13)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*O13)/2,0),ROUND((L13*M13*O13),0))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="37">
+        <f>IF(AND(B13="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R13" s="38">
+        <f>pax_cap*Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="36">
+        <f>R13*P13</f>
+        <v/>
+      </c>
+      <c r="T13" s="39">
+        <f>E13*discount</f>
+        <v/>
+      </c>
+      <c r="U13" s="40">
+        <f>T13*S13</f>
+        <v/>
+      </c>
+      <c r="V13" s="40">
+        <f>(battery/range_nm)*D13*P13*VLOOKUP(B13,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W13" s="40">
+        <f>VLOOKUP(B13,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X13" s="40">
+        <f>VLOOKUP(B13,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z13" s="40">
+        <f>VLOOKUP(B13,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA13" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB13" s="40">
+        <f>V13+W13+X13+Y13+Z13+AA13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="40">
+        <f>VLOOKUP(B13,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD13" s="40">
+        <f>U13-AB13</f>
+        <v/>
+      </c>
+      <c r="AE13" s="37">
+        <f>IF(U13=0,"",AD13/U13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="38">
+        <f>IF(AD13&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/AD13)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="35">
+        <f>((D13*P13/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D13*P13*VLOOKUP(B13,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH13" s="33" t="n">
+        <v>3890964</v>
+      </c>
+      <c r="AI13" s="34" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AJ13" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AK13" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL13" s="36">
+        <f>IF(AH13="","",AH13*AK13)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="36">
+        <f>IF(OR(AH13="",S13=0),"",MIN(IF(AU13="",9.9E+99,AU13),FLOOR(AL13/S13,1)))</f>
+        <v/>
+      </c>
+      <c r="AN13" s="40">
+        <f>IF(AM13="","",AM13*IF(ABS(MOD(ABS((U13)),1)-0.5)&lt;1E-9,2*ROUND((U13)/2,0),ROUND((U13),0)))</f>
+        <v/>
+      </c>
+      <c r="AO13" s="38">
+        <f>IF(OR(AH13="",S13=0),"",MIN(IF(AU13="",9.9E+99,AU13),AL13/S13))</f>
+        <v/>
+      </c>
+      <c r="AP13" s="40">
+        <f>IF(AO13="","",AO13*IF(B13="South Korea",IF(ABS(MOD(ABS((U13)),1)-0.5)&lt;1E-9,2*ROUND((U13)/2,0),ROUND((U13),0)),U13))</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="42" t="n"/>
+      <c r="AR13" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS13" s="43" t="n"/>
+      <c r="AT13" s="43" t="n"/>
+      <c r="AU13" s="44" t="n"/>
+      <c r="AV13" s="45">
+        <f>IF(((T13*pax_cap*load_thin*IF(ABS(MOD(ABS((L13*M13*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_thin)/2,0),ROUND((L13*M13*revleg_thin),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_thin)/2,0),ROUND((L13*M13*revleg_thin),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((T13*pax_cap*load_thin*IF(ABS(MOD(ABS((L13*M13*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_thin)/2,0),ROUND((L13*M13*revleg_thin),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_thin)/2,0),ROUND((L13*M13*revleg_thin),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13)))</f>
+        <v/>
+      </c>
+      <c r="AW13" s="45">
+        <f>IF(((T13*pax_cap*IF(B13="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((T13*pax_cap*IF(B13="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L13*M13*IF(B13="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13)))</f>
+        <v/>
+      </c>
+      <c r="AX13" s="45">
+        <f>IF(((T13*pax_cap*load_full*IF(ABS(MOD(ABS((L13*M13*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_full)/2,0),ROUND((L13*M13*revleg_full),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_full)/2,0),ROUND((L13*M13*revleg_full),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((T13*pax_cap*load_full*IF(ABS(MOD(ABS((L13*M13*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_full)/2,0),ROUND((L13*M13*revleg_full),0)))-(((battery/range_nm)*D13*IF(ABS(MOD(ABS((L13*M13*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L13*M13*revleg_full)/2,0),ROUND((L13*M13*revleg_full),0))*VLOOKUP(B13,country_opex,3,FALSE))+W13+X13+Y13+Z13+AA13)))</f>
+        <v/>
+      </c>
+      <c r="AY13" s="46" t="n"/>
+      <c r="AZ13" s="46" t="inlineStr">
+        <is>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
+        </is>
+      </c>
+      <c r="BA13" s="34" t="inlineStr">
+        <is>
+          <t>rn-36dcca92d821</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="35">
+        <f>60*D14/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f>IF(B14="South Korea",D14/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="35">
+        <f>IF(B14="South Korea",I14+korea_turn_min+korea_dwell_min+J14,I14+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L14" s="36">
+        <f>IF(B14="South Korea",FLOOR(60*korea_service_hr/K14,1),MIN(15,FLOOR(60*service_hr/K14,1)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H14)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H14)/2,0),ROUND((365*mech_uptime*H14),0))</f>
+        <v/>
+      </c>
+      <c r="N14" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O14" s="37">
+        <f>IF(AND(B14="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P14" s="36">
+        <f>IF(ABS(MOD(ABS((L14*M14*O14)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*O14)/2,0),ROUND((L14*M14*O14),0))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="37">
+        <f>IF(AND(B14="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R14" s="38">
+        <f>pax_cap*Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="36">
+        <f>R14*P14</f>
+        <v/>
+      </c>
+      <c r="T14" s="39">
+        <f>E14*discount</f>
+        <v/>
+      </c>
+      <c r="U14" s="40">
+        <f>T14*S14</f>
+        <v/>
+      </c>
+      <c r="V14" s="40">
+        <f>(battery/range_nm)*D14*P14*VLOOKUP(B14,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W14" s="40">
+        <f>VLOOKUP(B14,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X14" s="40">
+        <f>VLOOKUP(B14,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z14" s="40">
+        <f>VLOOKUP(B14,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA14" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB14" s="40">
+        <f>V14+W14+X14+Y14+Z14+AA14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="40">
+        <f>VLOOKUP(B14,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD14" s="40">
+        <f>U14-AB14</f>
+        <v/>
+      </c>
+      <c r="AE14" s="37">
+        <f>IF(U14=0,"",AD14/U14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="38">
+        <f>IF(AD14&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/AD14)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="35">
+        <f>((D14*P14/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D14*P14*VLOOKUP(B14,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH14" s="33" t="n">
+        <v>6100556</v>
+      </c>
+      <c r="AI14" s="34" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AJ14" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AK14" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL14" s="36">
+        <f>IF(AH14="","",AH14*AK14)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="36">
+        <f>IF(OR(AH14="",S14=0),"",MIN(IF(AU14="",9.9E+99,AU14),FLOOR(AL14/S14,1)))</f>
+        <v/>
+      </c>
+      <c r="AN14" s="40">
+        <f>IF(AM14="","",AM14*IF(ABS(MOD(ABS((U14)),1)-0.5)&lt;1E-9,2*ROUND((U14)/2,0),ROUND((U14),0)))</f>
+        <v/>
+      </c>
+      <c r="AO14" s="38">
+        <f>IF(OR(AH14="",S14=0),"",MIN(IF(AU14="",9.9E+99,AU14),AL14/S14))</f>
+        <v/>
+      </c>
+      <c r="AP14" s="40">
+        <f>IF(AO14="","",AO14*IF(B14="South Korea",IF(ABS(MOD(ABS((U14)),1)-0.5)&lt;1E-9,2*ROUND((U14)/2,0),ROUND((U14),0)),U14))</f>
+        <v/>
+      </c>
+      <c r="AQ14" s="42" t="n"/>
+      <c r="AR14" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS14" s="43" t="n"/>
+      <c r="AT14" s="43" t="n"/>
+      <c r="AU14" s="44" t="n"/>
+      <c r="AV14" s="45">
+        <f>IF(((T14*pax_cap*load_thin*IF(ABS(MOD(ABS((L14*M14*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_thin)/2,0),ROUND((L14*M14*revleg_thin),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_thin)/2,0),ROUND((L14*M14*revleg_thin),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((T14*pax_cap*load_thin*IF(ABS(MOD(ABS((L14*M14*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_thin)/2,0),ROUND((L14*M14*revleg_thin),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_thin)/2,0),ROUND((L14*M14*revleg_thin),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14)))</f>
+        <v/>
+      </c>
+      <c r="AW14" s="45">
+        <f>IF(((T14*pax_cap*IF(B14="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((T14*pax_cap*IF(B14="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L14*M14*IF(B14="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14)))</f>
+        <v/>
+      </c>
+      <c r="AX14" s="45">
+        <f>IF(((T14*pax_cap*load_full*IF(ABS(MOD(ABS((L14*M14*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_full)/2,0),ROUND((L14*M14*revleg_full),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_full)/2,0),ROUND((L14*M14*revleg_full),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((T14*pax_cap*load_full*IF(ABS(MOD(ABS((L14*M14*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_full)/2,0),ROUND((L14*M14*revleg_full),0)))-(((battery/range_nm)*D14*IF(ABS(MOD(ABS((L14*M14*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L14*M14*revleg_full)/2,0),ROUND((L14*M14*revleg_full),0))*VLOOKUP(B14,country_opex,3,FALSE))+W14+X14+Y14+Z14+AA14)))</f>
+        <v/>
+      </c>
+      <c r="AY14" s="46" t="n"/>
+      <c r="AZ14" s="46" t="inlineStr">
+        <is>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
+        </is>
+      </c>
+      <c r="BA14" s="34" t="inlineStr">
+        <is>
+          <t>rn-7d157e1300da</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="35">
+        <f>60*D15/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>IF(B15="South Korea",D15/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="35">
+        <f>IF(B15="South Korea",I15+korea_turn_min+korea_dwell_min+J15,I15+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L15" s="36">
+        <f>IF(B15="South Korea",FLOOR(60*korea_service_hr/K15,1),MIN(15,FLOOR(60*service_hr/K15,1)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H15)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H15)/2,0),ROUND((365*mech_uptime*H15),0))</f>
+        <v/>
+      </c>
+      <c r="N15" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O15" s="37">
+        <f>IF(AND(B15="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P15" s="36">
+        <f>IF(ABS(MOD(ABS((L15*M15*O15)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*O15)/2,0),ROUND((L15*M15*O15),0))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="37">
+        <f>IF(AND(B15="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R15" s="38">
+        <f>pax_cap*Q15</f>
+        <v/>
+      </c>
+      <c r="S15" s="36">
+        <f>R15*P15</f>
+        <v/>
+      </c>
+      <c r="T15" s="39">
+        <f>E15*discount</f>
+        <v/>
+      </c>
+      <c r="U15" s="40">
+        <f>T15*S15</f>
+        <v/>
+      </c>
+      <c r="V15" s="40">
+        <f>(battery/range_nm)*D15*P15*VLOOKUP(B15,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W15" s="40">
+        <f>VLOOKUP(B15,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X15" s="40">
+        <f>VLOOKUP(B15,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z15" s="40">
+        <f>VLOOKUP(B15,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA15" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB15" s="40">
+        <f>V15+W15+X15+Y15+Z15+AA15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="40">
+        <f>VLOOKUP(B15,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD15" s="40">
+        <f>U15-AB15</f>
+        <v/>
+      </c>
+      <c r="AE15" s="37">
+        <f>IF(U15=0,"",AD15/U15)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="38">
+        <f>IF(AD15&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/AD15)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="35">
+        <f>((D15*P15/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D15*P15*VLOOKUP(B15,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH15" s="33" t="n">
+        <v>278607</v>
+      </c>
+      <c r="AI15" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ15" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK15" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL15" s="36">
+        <f>IF(AH15="","",AH15*AK15)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="36">
+        <f>IF(OR(AH15="",S15=0),"",MIN(IF(AU15="",9.9E+99,AU15),FLOOR(AL15/S15,1)))</f>
+        <v/>
+      </c>
+      <c r="AN15" s="40">
+        <f>IF(AM15="","",AM15*IF(ABS(MOD(ABS((U15)),1)-0.5)&lt;1E-9,2*ROUND((U15)/2,0),ROUND((U15),0)))</f>
+        <v/>
+      </c>
+      <c r="AO15" s="38">
+        <f>IF(OR(AH15="",S15=0),"",MIN(IF(AU15="",9.9E+99,AU15),AL15/S15))</f>
+        <v/>
+      </c>
+      <c r="AP15" s="40">
+        <f>IF(AO15="","",AO15*IF(B15="South Korea",IF(ABS(MOD(ABS((U15)),1)-0.5)&lt;1E-9,2*ROUND((U15)/2,0),ROUND((U15),0)),U15))</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="42" t="n"/>
+      <c r="AR15" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS15" s="43" t="n"/>
+      <c r="AT15" s="43" t="n"/>
+      <c r="AU15" s="44" t="n"/>
+      <c r="AV15" s="45">
+        <f>IF(((T15*pax_cap*load_thin*IF(ABS(MOD(ABS((L15*M15*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_thin)/2,0),ROUND((L15*M15*revleg_thin),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_thin)/2,0),ROUND((L15*M15*revleg_thin),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((T15*pax_cap*load_thin*IF(ABS(MOD(ABS((L15*M15*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_thin)/2,0),ROUND((L15*M15*revleg_thin),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_thin)/2,0),ROUND((L15*M15*revleg_thin),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15)))</f>
+        <v/>
+      </c>
+      <c r="AW15" s="45">
+        <f>IF(((T15*pax_cap*IF(B15="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((T15*pax_cap*IF(B15="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L15*M15*IF(B15="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15)))</f>
+        <v/>
+      </c>
+      <c r="AX15" s="45">
+        <f>IF(((T15*pax_cap*load_full*IF(ABS(MOD(ABS((L15*M15*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_full)/2,0),ROUND((L15*M15*revleg_full),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_full)/2,0),ROUND((L15*M15*revleg_full),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((T15*pax_cap*load_full*IF(ABS(MOD(ABS((L15*M15*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_full)/2,0),ROUND((L15*M15*revleg_full),0)))-(((battery/range_nm)*D15*IF(ABS(MOD(ABS((L15*M15*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L15*M15*revleg_full)/2,0),ROUND((L15*M15*revleg_full),0))*VLOOKUP(B15,country_opex,3,FALSE))+W15+X15+Y15+Z15+AA15)))</f>
+        <v/>
+      </c>
+      <c r="AY15" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ15" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
+      <c r="BA15" s="34" t="inlineStr">
+        <is>
+          <t>rn-369ef0eb69d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Terminal São Joaquim (Salvador ferry-boat) → Terminal Marítimo de Bom Despacho (Itaparica)</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="35">
+        <f>60*D16/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J16" s="35">
+        <f>IF(B16="South Korea",D16/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="35">
+        <f>IF(B16="South Korea",I16+korea_turn_min+korea_dwell_min+J16,I16+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L16" s="36">
+        <f>IF(B16="South Korea",FLOOR(60*korea_service_hr/K16,1),MIN(15,FLOOR(60*service_hr/K16,1)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H16)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H16)/2,0),ROUND((365*mech_uptime*H16),0))</f>
+        <v/>
+      </c>
+      <c r="N16" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O16" s="37">
+        <f>IF(AND(B16="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P16" s="36">
+        <f>IF(ABS(MOD(ABS((L16*M16*O16)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*O16)/2,0),ROUND((L16*M16*O16),0))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="37">
+        <f>IF(AND(B16="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R16" s="38">
+        <f>pax_cap*Q16</f>
+        <v/>
+      </c>
+      <c r="S16" s="36">
+        <f>R16*P16</f>
+        <v/>
+      </c>
+      <c r="T16" s="39">
+        <f>E16*discount</f>
+        <v/>
+      </c>
+      <c r="U16" s="40">
+        <f>T16*S16</f>
+        <v/>
+      </c>
+      <c r="V16" s="40">
+        <f>(battery/range_nm)*D16*P16*VLOOKUP(B16,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W16" s="40">
+        <f>VLOOKUP(B16,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X16" s="40">
+        <f>VLOOKUP(B16,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z16" s="40">
+        <f>VLOOKUP(B16,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA16" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB16" s="40">
+        <f>V16+W16+X16+Y16+Z16+AA16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="40">
+        <f>VLOOKUP(B16,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD16" s="40">
+        <f>U16-AB16</f>
+        <v/>
+      </c>
+      <c r="AE16" s="37">
+        <f>IF(U16=0,"",AD16/U16)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="38">
+        <f>IF(AD16&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/AD16)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="35">
+        <f>((D16*P16/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D16*P16*VLOOKUP(B16,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH16" s="33" t="n">
+        <v>7490000</v>
+      </c>
+      <c r="AI16" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="AJ16" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK16" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL16" s="36">
+        <f>IF(AH16="","",AH16*AK16)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="36">
+        <f>IF(OR(AH16="",S16=0),"",MIN(IF(AU16="",9.9E+99,AU16),FLOOR(AL16/S16,1)))</f>
+        <v/>
+      </c>
+      <c r="AN16" s="40">
+        <f>IF(AM16="","",AM16*IF(ABS(MOD(ABS((U16)),1)-0.5)&lt;1E-9,2*ROUND((U16)/2,0),ROUND((U16),0)))</f>
+        <v/>
+      </c>
+      <c r="AO16" s="38">
+        <f>IF(OR(AH16="",S16=0),"",MIN(IF(AU16="",9.9E+99,AU16),AL16/S16))</f>
+        <v/>
+      </c>
+      <c r="AP16" s="40">
+        <f>IF(AO16="","",AO16*IF(B16="South Korea",IF(ABS(MOD(ABS((U16)),1)-0.5)&lt;1E-9,2*ROUND((U16)/2,0),ROUND((U16),0)),U16))</f>
+        <v/>
+      </c>
+      <c r="AQ16" s="42" t="n"/>
+      <c r="AR16" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS16" s="43" t="n"/>
+      <c r="AT16" s="43" t="n"/>
+      <c r="AU16" s="44" t="n"/>
+      <c r="AV16" s="45">
+        <f>IF(((T16*pax_cap*load_thin*IF(ABS(MOD(ABS((L16*M16*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_thin)/2,0),ROUND((L16*M16*revleg_thin),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_thin)/2,0),ROUND((L16*M16*revleg_thin),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((T16*pax_cap*load_thin*IF(ABS(MOD(ABS((L16*M16*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_thin)/2,0),ROUND((L16*M16*revleg_thin),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_thin)/2,0),ROUND((L16*M16*revleg_thin),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16)))</f>
+        <v/>
+      </c>
+      <c r="AW16" s="45">
+        <f>IF(((T16*pax_cap*IF(B16="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((T16*pax_cap*IF(B16="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L16*M16*IF(B16="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16)))</f>
+        <v/>
+      </c>
+      <c r="AX16" s="45">
+        <f>IF(((T16*pax_cap*load_full*IF(ABS(MOD(ABS((L16*M16*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_full)/2,0),ROUND((L16*M16*revleg_full),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_full)/2,0),ROUND((L16*M16*revleg_full),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((T16*pax_cap*load_full*IF(ABS(MOD(ABS((L16*M16*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_full)/2,0),ROUND((L16*M16*revleg_full),0)))-(((battery/range_nm)*D16*IF(ABS(MOD(ABS((L16*M16*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L16*M16*revleg_full)/2,0),ROUND((L16*M16*revleg_full),0))*VLOOKUP(B16,country_opex,3,FALSE))+W16+X16+Y16+Z16+AA16)))</f>
+        <v/>
+      </c>
+      <c r="AY16" s="46" t="inlineStr">
+        <is>
+          <t>AGERBA Resolução Nº 11 (2026-03-03) tariff table, in force 2026-03-06</t>
+        </is>
+      </c>
+      <c r="AZ16" s="46" t="inlineStr">
+        <is>
+          <t>Ministério do Turismo figures released at the Salvador–Itaparica bridge groundbreaking (2026-07-01), via Diário do Turismo 2026-07-03; Jan–May 2026 = 3.42M (~8.2M annualized run-rate) corroborates.</t>
+        </is>
+      </c>
+      <c r="BA16" s="34" t="inlineStr">
+        <is>
+          <t>rn-4aa1660ff921</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="35">
+        <f>60*D17/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J17" s="35">
+        <f>IF(B17="South Korea",D17/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="35">
+        <f>IF(B17="South Korea",I17+korea_turn_min+korea_dwell_min+J17,I17+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L17" s="36">
+        <f>IF(B17="South Korea",FLOOR(60*korea_service_hr/K17,1),MIN(15,FLOOR(60*service_hr/K17,1)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H17)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H17)/2,0),ROUND((365*mech_uptime*H17),0))</f>
+        <v/>
+      </c>
+      <c r="N17" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O17" s="37">
+        <f>IF(AND(B17="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P17" s="36">
+        <f>IF(ABS(MOD(ABS((L17*M17*O17)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*O17)/2,0),ROUND((L17*M17*O17),0))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="37">
+        <f>IF(AND(B17="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R17" s="38">
+        <f>pax_cap*Q17</f>
+        <v/>
+      </c>
+      <c r="S17" s="36">
+        <f>R17*P17</f>
+        <v/>
+      </c>
+      <c r="T17" s="39">
+        <f>E17*discount</f>
+        <v/>
+      </c>
+      <c r="U17" s="40">
+        <f>T17*S17</f>
+        <v/>
+      </c>
+      <c r="V17" s="40">
+        <f>(battery/range_nm)*D17*P17*VLOOKUP(B17,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W17" s="40">
+        <f>VLOOKUP(B17,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X17" s="40">
+        <f>VLOOKUP(B17,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z17" s="40">
+        <f>VLOOKUP(B17,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA17" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB17" s="40">
+        <f>V17+W17+X17+Y17+Z17+AA17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="40">
+        <f>VLOOKUP(B17,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD17" s="40">
+        <f>U17-AB17</f>
+        <v/>
+      </c>
+      <c r="AE17" s="37">
+        <f>IF(U17=0,"",AD17/U17)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="38">
+        <f>IF(AD17&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/AD17)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="35">
+        <f>((D17*P17/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D17*P17*VLOOKUP(B17,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH17" s="33" t="n">
+        <v>1170652</v>
+      </c>
+      <c r="AI17" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ17" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK17" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL17" s="36">
+        <f>IF(AH17="","",AH17*AK17)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="36">
+        <f>IF(OR(AH17="",S17=0),"",MIN(IF(AU17="",9.9E+99,AU17),FLOOR(AL17/S17,1)))</f>
+        <v/>
+      </c>
+      <c r="AN17" s="40">
+        <f>IF(AM17="","",AM17*IF(ABS(MOD(ABS((U17)),1)-0.5)&lt;1E-9,2*ROUND((U17)/2,0),ROUND((U17),0)))</f>
+        <v/>
+      </c>
+      <c r="AO17" s="38">
+        <f>IF(OR(AH17="",S17=0),"",MIN(IF(AU17="",9.9E+99,AU17),AL17/S17))</f>
+        <v/>
+      </c>
+      <c r="AP17" s="40">
+        <f>IF(AO17="","",AO17*IF(B17="South Korea",IF(ABS(MOD(ABS((U17)),1)-0.5)&lt;1E-9,2*ROUND((U17)/2,0),ROUND((U17),0)),U17))</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="42" t="n"/>
+      <c r="AR17" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS17" s="43" t="n"/>
+      <c r="AT17" s="43" t="n"/>
+      <c r="AU17" s="44" t="n"/>
+      <c r="AV17" s="45">
+        <f>IF(((T17*pax_cap*load_thin*IF(ABS(MOD(ABS((L17*M17*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_thin)/2,0),ROUND((L17*M17*revleg_thin),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_thin)/2,0),ROUND((L17*M17*revleg_thin),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((T17*pax_cap*load_thin*IF(ABS(MOD(ABS((L17*M17*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_thin)/2,0),ROUND((L17*M17*revleg_thin),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_thin)/2,0),ROUND((L17*M17*revleg_thin),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17)))</f>
+        <v/>
+      </c>
+      <c r="AW17" s="45">
+        <f>IF(((T17*pax_cap*IF(B17="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((T17*pax_cap*IF(B17="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L17*M17*IF(B17="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17)))</f>
+        <v/>
+      </c>
+      <c r="AX17" s="45">
+        <f>IF(((T17*pax_cap*load_full*IF(ABS(MOD(ABS((L17*M17*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_full)/2,0),ROUND((L17*M17*revleg_full),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_full)/2,0),ROUND((L17*M17*revleg_full),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((T17*pax_cap*load_full*IF(ABS(MOD(ABS((L17*M17*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_full)/2,0),ROUND((L17*M17*revleg_full),0)))-(((battery/range_nm)*D17*IF(ABS(MOD(ABS((L17*M17*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L17*M17*revleg_full)/2,0),ROUND((L17*M17*revleg_full),0))*VLOOKUP(B17,country_opex,3,FALSE))+W17+X17+Y17+Z17+AA17)))</f>
+        <v/>
+      </c>
+      <c r="AY17" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ17" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
+      <c r="BA17" s="34" t="inlineStr">
+        <is>
+          <t>rn-00bb6ded4be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Angra dos Reis Terminal (Costa Verde) → Abraão Terminal (Ilha Grande)</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="35">
+        <f>60*D18/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J18" s="35">
+        <f>IF(B18="South Korea",D18/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="35">
+        <f>IF(B18="South Korea",I18+korea_turn_min+korea_dwell_min+J18,I18+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L18" s="36">
+        <f>IF(B18="South Korea",FLOOR(60*korea_service_hr/K18,1),MIN(15,FLOOR(60*service_hr/K18,1)))</f>
+        <v/>
+      </c>
+      <c r="M18" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H18)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H18)/2,0),ROUND((365*mech_uptime*H18),0))</f>
+        <v/>
+      </c>
+      <c r="N18" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O18" s="37">
+        <f>IF(AND(B18="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P18" s="36">
+        <f>IF(ABS(MOD(ABS((L18*M18*O18)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*O18)/2,0),ROUND((L18*M18*O18),0))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="37">
+        <f>IF(AND(B18="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R18" s="38">
+        <f>pax_cap*Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="36">
+        <f>R18*P18</f>
+        <v/>
+      </c>
+      <c r="T18" s="39">
+        <f>E18*discount</f>
+        <v/>
+      </c>
+      <c r="U18" s="40">
+        <f>T18*S18</f>
+        <v/>
+      </c>
+      <c r="V18" s="40">
+        <f>(battery/range_nm)*D18*P18*VLOOKUP(B18,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W18" s="40">
+        <f>VLOOKUP(B18,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X18" s="40">
+        <f>VLOOKUP(B18,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z18" s="40">
+        <f>VLOOKUP(B18,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA18" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB18" s="40">
+        <f>V18+W18+X18+Y18+Z18+AA18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="40">
+        <f>VLOOKUP(B18,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD18" s="40">
+        <f>U18-AB18</f>
+        <v/>
+      </c>
+      <c r="AE18" s="37">
+        <f>IF(U18=0,"",AD18/U18)</f>
+        <v/>
+      </c>
+      <c r="AF18" s="38">
+        <f>IF(AD18&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/AD18)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="35">
+        <f>((D18*P18/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D18*P18*VLOOKUP(B18,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH18" s="33" t="n">
+        <v>207993</v>
+      </c>
+      <c r="AI18" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ18" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK18" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL18" s="36">
+        <f>IF(AH18="","",AH18*AK18)</f>
+        <v/>
+      </c>
+      <c r="AM18" s="36">
+        <f>IF(OR(AH18="",S18=0),"",MIN(IF(AU18="",9.9E+99,AU18),FLOOR(AL18/S18,1)))</f>
+        <v/>
+      </c>
+      <c r="AN18" s="40">
+        <f>IF(AM18="","",AM18*IF(ABS(MOD(ABS((U18)),1)-0.5)&lt;1E-9,2*ROUND((U18)/2,0),ROUND((U18),0)))</f>
+        <v/>
+      </c>
+      <c r="AO18" s="38">
+        <f>IF(OR(AH18="",S18=0),"",MIN(IF(AU18="",9.9E+99,AU18),AL18/S18))</f>
+        <v/>
+      </c>
+      <c r="AP18" s="40">
+        <f>IF(AO18="","",AO18*IF(B18="South Korea",IF(ABS(MOD(ABS((U18)),1)-0.5)&lt;1E-9,2*ROUND((U18)/2,0),ROUND((U18),0)),U18))</f>
+        <v/>
+      </c>
+      <c r="AQ18" s="42" t="n"/>
+      <c r="AR18" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS18" s="43" t="n"/>
+      <c r="AT18" s="43" t="n"/>
+      <c r="AU18" s="44" t="n"/>
+      <c r="AV18" s="45">
+        <f>IF(((T18*pax_cap*load_thin*IF(ABS(MOD(ABS((L18*M18*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_thin)/2,0),ROUND((L18*M18*revleg_thin),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_thin)/2,0),ROUND((L18*M18*revleg_thin),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((T18*pax_cap*load_thin*IF(ABS(MOD(ABS((L18*M18*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_thin)/2,0),ROUND((L18*M18*revleg_thin),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_thin)/2,0),ROUND((L18*M18*revleg_thin),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18)))</f>
+        <v/>
+      </c>
+      <c r="AW18" s="45">
+        <f>IF(((T18*pax_cap*IF(B18="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((T18*pax_cap*IF(B18="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L18*M18*IF(B18="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18)))</f>
+        <v/>
+      </c>
+      <c r="AX18" s="45">
+        <f>IF(((T18*pax_cap*load_full*IF(ABS(MOD(ABS((L18*M18*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_full)/2,0),ROUND((L18*M18*revleg_full),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_full)/2,0),ROUND((L18*M18*revleg_full),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((T18*pax_cap*load_full*IF(ABS(MOD(ABS((L18*M18*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_full)/2,0),ROUND((L18*M18*revleg_full),0)))-(((battery/range_nm)*D18*IF(ABS(MOD(ABS((L18*M18*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L18*M18*revleg_full)/2,0),ROUND((L18*M18*revleg_full),0))*VLOOKUP(B18,country_opex,3,FALSE))+W18+X18+Y18+Z18+AA18)))</f>
+        <v/>
+      </c>
+      <c r="AY18" s="46" t="inlineStr">
+        <is>
+          <t>AGETRANSP / CCR Barcas Costa Verde published tariff</t>
+        </is>
+      </c>
+      <c r="AZ18" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
+      <c r="BA18" s="34" t="inlineStr">
+        <is>
+          <t>rn-7ec802385553</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Terminal Turístico Náutico da Bahia (Comércio) → Terminal Hidroviário de Morro de São Paulo (Cairu)</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="34" t="n"/>
+      <c r="H19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="35">
+        <f>60*D19/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J19" s="35">
+        <f>IF(B19="South Korea",D19/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="35">
+        <f>IF(B19="South Korea",I19+korea_turn_min+korea_dwell_min+J19,I19+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L19" s="36">
+        <f>IF(B19="South Korea",FLOOR(60*korea_service_hr/K19,1),MIN(15,FLOOR(60*service_hr/K19,1)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H19)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H19)/2,0),ROUND((365*mech_uptime*H19),0))</f>
+        <v/>
+      </c>
+      <c r="N19" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O19" s="37">
+        <f>IF(AND(B19="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P19" s="36">
+        <f>IF(ABS(MOD(ABS((L19*M19*O19)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*O19)/2,0),ROUND((L19*M19*O19),0))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="37">
+        <f>IF(AND(B19="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R19" s="38">
+        <f>pax_cap*Q19</f>
+        <v/>
+      </c>
+      <c r="S19" s="36">
+        <f>R19*P19</f>
+        <v/>
+      </c>
+      <c r="T19" s="39">
+        <f>E19*discount</f>
+        <v/>
+      </c>
+      <c r="U19" s="40">
+        <f>T19*S19</f>
+        <v/>
+      </c>
+      <c r="V19" s="40">
+        <f>(battery/range_nm)*D19*P19*VLOOKUP(B19,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W19" s="40">
+        <f>VLOOKUP(B19,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X19" s="40">
+        <f>VLOOKUP(B19,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z19" s="40">
+        <f>VLOOKUP(B19,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA19" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB19" s="40">
+        <f>V19+W19+X19+Y19+Z19+AA19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="40">
+        <f>VLOOKUP(B19,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD19" s="40">
+        <f>U19-AB19</f>
+        <v/>
+      </c>
+      <c r="AE19" s="37">
+        <f>IF(U19=0,"",AD19/U19)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="38">
+        <f>IF(AD19&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/AD19)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="35">
+        <f>((D19*P19/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D19*P19*VLOOKUP(B19,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH19" s="33" t="n"/>
+      <c r="AI19" s="34" t="n"/>
+      <c r="AJ19" s="34" t="n"/>
+      <c r="AK19" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL19" s="36">
+        <f>IF(AH19="","",AH19*AK19)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="36">
+        <f>IF(OR(AH19="",S19=0),"",MIN(IF(AU19="",9.9E+99,AU19),FLOOR(AL19/S19,1)))</f>
+        <v/>
+      </c>
+      <c r="AN19" s="40">
+        <f>IF(AM19="","",AM19*IF(ABS(MOD(ABS((U19)),1)-0.5)&lt;1E-9,2*ROUND((U19)/2,0),ROUND((U19),0)))</f>
+        <v/>
+      </c>
+      <c r="AO19" s="38">
+        <f>IF(OR(AH19="",S19=0),"",MIN(IF(AU19="",9.9E+99,AU19),AL19/S19))</f>
+        <v/>
+      </c>
+      <c r="AP19" s="40">
+        <f>IF(AO19="","",AO19*IF(B19="South Korea",IF(ABS(MOD(ABS((U19)),1)-0.5)&lt;1E-9,2*ROUND((U19)/2,0),ROUND((U19),0)),U19))</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="42" t="n"/>
+      <c r="AR19" s="34" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AS19" s="43" t="n"/>
+      <c r="AT19" s="43" t="n"/>
+      <c r="AU19" s="44" t="n"/>
+      <c r="AV19" s="45">
+        <f>IF(((T19*pax_cap*load_thin*IF(ABS(MOD(ABS((L19*M19*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_thin)/2,0),ROUND((L19*M19*revleg_thin),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_thin)/2,0),ROUND((L19*M19*revleg_thin),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((T19*pax_cap*load_thin*IF(ABS(MOD(ABS((L19*M19*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_thin)/2,0),ROUND((L19*M19*revleg_thin),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_thin)/2,0),ROUND((L19*M19*revleg_thin),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19)))</f>
+        <v/>
+      </c>
+      <c r="AW19" s="45">
+        <f>IF(((T19*pax_cap*IF(B19="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((T19*pax_cap*IF(B19="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L19*M19*IF(B19="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19)))</f>
+        <v/>
+      </c>
+      <c r="AX19" s="45">
+        <f>IF(((T19*pax_cap*load_full*IF(ABS(MOD(ABS((L19*M19*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_full)/2,0),ROUND((L19*M19*revleg_full),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_full)/2,0),ROUND((L19*M19*revleg_full),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((T19*pax_cap*load_full*IF(ABS(MOD(ABS((L19*M19*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_full)/2,0),ROUND((L19*M19*revleg_full),0)))-(((battery/range_nm)*D19*IF(ABS(MOD(ABS((L19*M19*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L19*M19*revleg_full)/2,0),ROUND((L19*M19*revleg_full),0))*VLOOKUP(B19,country_opex,3,FALSE))+W19+X19+Y19+Z19+AA19)))</f>
+        <v/>
+      </c>
+      <c r="AY19" s="46" t="n"/>
+      <c r="AZ19" s="46" t="n"/>
+      <c r="BA19" s="34" t="inlineStr">
+        <is>
+          <t>rn-8dbc3663c115</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="35">
+        <f>60*D20/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J20" s="35">
+        <f>IF(B20="South Korea",D20/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="35">
+        <f>IF(B20="South Korea",I20+korea_turn_min+korea_dwell_min+J20,I20+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L20" s="36">
+        <f>IF(B20="South Korea",FLOOR(60*korea_service_hr/K20,1),MIN(15,FLOOR(60*service_hr/K20,1)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H20)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H20)/2,0),ROUND((365*mech_uptime*H20),0))</f>
+        <v/>
+      </c>
+      <c r="N20" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O20" s="37">
+        <f>IF(AND(B20="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P20" s="36">
+        <f>IF(ABS(MOD(ABS((L20*M20*O20)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*O20)/2,0),ROUND((L20*M20*O20),0))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="37">
+        <f>IF(AND(B20="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R20" s="38">
+        <f>pax_cap*Q20</f>
+        <v/>
+      </c>
+      <c r="S20" s="36">
+        <f>R20*P20</f>
+        <v/>
+      </c>
+      <c r="T20" s="39">
+        <f>E20*discount</f>
+        <v/>
+      </c>
+      <c r="U20" s="40">
+        <f>T20*S20</f>
+        <v/>
+      </c>
+      <c r="V20" s="40">
+        <f>(battery/range_nm)*D20*P20*VLOOKUP(B20,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W20" s="40">
+        <f>VLOOKUP(B20,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X20" s="40">
+        <f>VLOOKUP(B20,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z20" s="40">
+        <f>VLOOKUP(B20,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA20" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB20" s="40">
+        <f>V20+W20+X20+Y20+Z20+AA20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="40">
+        <f>VLOOKUP(B20,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD20" s="40">
+        <f>U20-AB20</f>
+        <v/>
+      </c>
+      <c r="AE20" s="37">
+        <f>IF(U20=0,"",AD20/U20)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="38">
+        <f>IF(AD20&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/AD20)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="35">
+        <f>((D20*P20/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D20*P20*VLOOKUP(B20,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH20" s="33" t="n">
+        <v>187512</v>
+      </c>
+      <c r="AI20" s="34" t="n"/>
+      <c r="AJ20" s="34" t="n"/>
+      <c r="AK20" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL20" s="36">
+        <f>IF(AH20="","",AH20*AK20)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="36">
+        <f>IF(OR(AH20="",S20=0),"",MIN(IF(AU20="",9.9E+99,AU20),FLOOR(AL20/S20,1)))</f>
+        <v/>
+      </c>
+      <c r="AN20" s="40">
+        <f>IF(AM20="","",AM20*IF(ABS(MOD(ABS((U20)),1)-0.5)&lt;1E-9,2*ROUND((U20)/2,0),ROUND((U20),0)))</f>
+        <v/>
+      </c>
+      <c r="AO20" s="38">
+        <f>IF(OR(AH20="",S20=0),"",MIN(IF(AU20="",9.9E+99,AU20),AL20/S20))</f>
+        <v/>
+      </c>
+      <c r="AP20" s="40">
+        <f>IF(AO20="","",AO20*IF(B20="South Korea",IF(ABS(MOD(ABS((U20)),1)-0.5)&lt;1E-9,2*ROUND((U20)/2,0),ROUND((U20),0)),U20))</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="42" t="n"/>
+      <c r="AR20" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS20" s="43" t="n"/>
+      <c r="AT20" s="43" t="n"/>
+      <c r="AU20" s="44" t="n"/>
+      <c r="AV20" s="45">
+        <f>IF(((T20*pax_cap*load_thin*IF(ABS(MOD(ABS((L20*M20*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_thin)/2,0),ROUND((L20*M20*revleg_thin),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_thin)/2,0),ROUND((L20*M20*revleg_thin),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((T20*pax_cap*load_thin*IF(ABS(MOD(ABS((L20*M20*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_thin)/2,0),ROUND((L20*M20*revleg_thin),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_thin)/2,0),ROUND((L20*M20*revleg_thin),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20)))</f>
+        <v/>
+      </c>
+      <c r="AW20" s="45">
+        <f>IF(((T20*pax_cap*IF(B20="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((T20*pax_cap*IF(B20="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L20*M20*IF(B20="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20)))</f>
+        <v/>
+      </c>
+      <c r="AX20" s="45">
+        <f>IF(((T20*pax_cap*load_full*IF(ABS(MOD(ABS((L20*M20*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_full)/2,0),ROUND((L20*M20*revleg_full),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_full)/2,0),ROUND((L20*M20*revleg_full),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((T20*pax_cap*load_full*IF(ABS(MOD(ABS((L20*M20*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_full)/2,0),ROUND((L20*M20*revleg_full),0)))-(((battery/range_nm)*D20*IF(ABS(MOD(ABS((L20*M20*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L20*M20*revleg_full)/2,0),ROUND((L20*M20*revleg_full),0))*VLOOKUP(B20,country_opex,3,FALSE))+W20+X20+Y20+Z20+AA20)))</f>
+        <v/>
+      </c>
+      <c r="AY20" s="46" t="n"/>
+      <c r="AZ20" s="46" t="n"/>
+      <c r="BA20" s="34" t="inlineStr">
+        <is>
+          <t>rn-b06f6971ed47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="34" t="n"/>
+      <c r="H21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="35">
+        <f>60*D21/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J21" s="35">
+        <f>IF(B21="South Korea",D21/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="35">
+        <f>IF(B21="South Korea",I21+korea_turn_min+korea_dwell_min+J21,I21+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L21" s="36">
+        <f>IF(B21="South Korea",FLOOR(60*korea_service_hr/K21,1),MIN(15,FLOOR(60*service_hr/K21,1)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H21)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H21)/2,0),ROUND((365*mech_uptime*H21),0))</f>
+        <v/>
+      </c>
+      <c r="N21" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O21" s="37">
+        <f>IF(AND(B21="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P21" s="36">
+        <f>IF(ABS(MOD(ABS((L21*M21*O21)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*O21)/2,0),ROUND((L21*M21*O21),0))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="37">
+        <f>IF(AND(B21="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R21" s="38">
+        <f>pax_cap*Q21</f>
+        <v/>
+      </c>
+      <c r="S21" s="36">
+        <f>R21*P21</f>
+        <v/>
+      </c>
+      <c r="T21" s="39">
+        <f>E21*discount</f>
+        <v/>
+      </c>
+      <c r="U21" s="40">
+        <f>T21*S21</f>
+        <v/>
+      </c>
+      <c r="V21" s="40">
+        <f>(battery/range_nm)*D21*P21*VLOOKUP(B21,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W21" s="40">
+        <f>VLOOKUP(B21,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X21" s="40">
+        <f>VLOOKUP(B21,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z21" s="40">
+        <f>VLOOKUP(B21,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA21" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB21" s="40">
+        <f>V21+W21+X21+Y21+Z21+AA21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="40">
+        <f>VLOOKUP(B21,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD21" s="40">
+        <f>U21-AB21</f>
+        <v/>
+      </c>
+      <c r="AE21" s="37">
+        <f>IF(U21=0,"",AD21/U21)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="38">
+        <f>IF(AD21&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/AD21)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="35">
+        <f>((D21*P21/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D21*P21*VLOOKUP(B21,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH21" s="33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AI21" s="34" t="n"/>
+      <c r="AJ21" s="34" t="n"/>
+      <c r="AK21" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL21" s="36">
+        <f>IF(AH21="","",AH21*AK21)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="36">
+        <f>IF(OR(AH21="",S21=0),"",MIN(IF(AU21="",9.9E+99,AU21),FLOOR(AL21/S21,1)))</f>
+        <v/>
+      </c>
+      <c r="AN21" s="40">
+        <f>IF(AM21="","",AM21*IF(ABS(MOD(ABS((U21)),1)-0.5)&lt;1E-9,2*ROUND((U21)/2,0),ROUND((U21),0)))</f>
+        <v/>
+      </c>
+      <c r="AO21" s="38">
+        <f>IF(OR(AH21="",S21=0),"",MIN(IF(AU21="",9.9E+99,AU21),AL21/S21))</f>
+        <v/>
+      </c>
+      <c r="AP21" s="40">
+        <f>IF(AO21="","",AO21*IF(B21="South Korea",IF(ABS(MOD(ABS((U21)),1)-0.5)&lt;1E-9,2*ROUND((U21)/2,0),ROUND((U21),0)),U21))</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="42" t="n"/>
+      <c r="AR21" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS21" s="43" t="n"/>
+      <c r="AT21" s="43" t="n"/>
+      <c r="AU21" s="44" t="n"/>
+      <c r="AV21" s="45">
+        <f>IF(((T21*pax_cap*load_thin*IF(ABS(MOD(ABS((L21*M21*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_thin)/2,0),ROUND((L21*M21*revleg_thin),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_thin)/2,0),ROUND((L21*M21*revleg_thin),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((T21*pax_cap*load_thin*IF(ABS(MOD(ABS((L21*M21*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_thin)/2,0),ROUND((L21*M21*revleg_thin),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_thin)/2,0),ROUND((L21*M21*revleg_thin),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21)))</f>
+        <v/>
+      </c>
+      <c r="AW21" s="45">
+        <f>IF(((T21*pax_cap*IF(B21="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((T21*pax_cap*IF(B21="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L21*M21*IF(B21="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21)))</f>
+        <v/>
+      </c>
+      <c r="AX21" s="45">
+        <f>IF(((T21*pax_cap*load_full*IF(ABS(MOD(ABS((L21*M21*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_full)/2,0),ROUND((L21*M21*revleg_full),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_full)/2,0),ROUND((L21*M21*revleg_full),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((T21*pax_cap*load_full*IF(ABS(MOD(ABS((L21*M21*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_full)/2,0),ROUND((L21*M21*revleg_full),0)))-(((battery/range_nm)*D21*IF(ABS(MOD(ABS((L21*M21*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L21*M21*revleg_full)/2,0),ROUND((L21*M21*revleg_full),0))*VLOOKUP(B21,country_opex,3,FALSE))+W21+X21+Y21+Z21+AA21)))</f>
+        <v/>
+      </c>
+      <c r="AY21" s="46" t="n"/>
+      <c r="AZ21" s="46" t="n"/>
+      <c r="BA21" s="34" t="inlineStr">
+        <is>
           <t>rn-c16a1627130f</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="U13" s="48">
-        <f>SUM(U4:U12)</f>
-        <v/>
-      </c>
-      <c r="AD13" s="48">
-        <f>SUM(AD4:AD12)</f>
-        <v/>
-      </c>
-      <c r="AE13" s="49">
-        <f>IF(U13=0,"",AD13/U13)</f>
-        <v/>
-      </c>
-      <c r="AM13" s="50">
-        <f>SUM(AM4:AM12)</f>
-        <v/>
-      </c>
-      <c r="AN13" s="48">
-        <f>SUM(AN4:AN12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="U22" s="48">
+        <f>SUM(U4:U21)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="48">
+        <f>SUM(AD4:AD21)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="49">
+        <f>IF(U22=0,"",AD22/U22)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="50">
+        <f>SUM(AM4:AM21)</f>
+        <v/>
+      </c>
+      <c r="AN22" s="48">
+        <f>SUM(AN4:AN21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Indrive Brazil</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>per_corridor_floor</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="51">
-        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E17" s="52">
-        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="D26" s="51">
+        <f>SUMIFS(AM4:AM21,A4:A21,"Indrive Brazil",AQ4:AQ21,"=",AR4:AR21,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E26" s="52">
+        <f>SUMIFS(AN4:AN21,A4:A21,"Indrive Brazil",AQ4:AQ21,"=",AR4:AR21,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Indrive Egypt</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>two luxury-belt captive routes on labeled destination-pool demand at ~90% floor capture; three held</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="51">
-        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E18" s="52">
-        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="D27" s="51">
+        <f>SUMIFS(AM4:AM21,A4:A21,"Indrive Egypt",AQ4:AQ21,"=",AR4:AR21,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E27" s="52">
+        <f>SUMIFS(AN4:AN21,A4:A21,"Indrive Egypt",AQ4:AQ21,"=",AR4:AR21,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D19" s="50">
-        <f>SUM(D17:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="48">
-        <f>SUM(E17:E18)</f>
+      <c r="D28" s="50">
+        <f>SUM(D26:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="48">
+        <f>SUM(E26:E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D29" s="53">
+        <f>SUMIF(AR4:AR21,"Estimated",AM4:AM21)</f>
+        <v/>
+      </c>
+      <c r="E29" s="54">
+        <f>SUMIF(AR4:AR21,"Estimated",AN4:AN21)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4791,8 +6580,8 @@
           <t>SOM capture rate (floor)</t>
         </is>
       </c>
-      <c r="C11" s="53">
-        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0))</f>
+      <c r="C11" s="55">
+        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$21="Grounded"),'Corridor economics'!$AH$4:$AH$21,'Corridor economics'!$E$4:$E$21),0))</f>
         <v/>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -4858,7 +6647,7 @@
         </is>
       </c>
       <c r="C16" s="52">
-        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0)</f>
+        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$21="Grounded"),'Corridor economics'!$AH$4:$AH$21,'Corridor economics'!$E$4:$E$21),0)</f>
         <v/>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -5036,12 +6825,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="57" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
